--- a/data/trans_orig/IP05A07-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP05A07-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14684</t>
+          <t>15040</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26451</t>
+          <t>27121</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14198</t>
+          <t>14598</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26759</t>
+          <t>27020</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31667</t>
+          <t>32265</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48701</t>
+          <t>49180</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,23%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19819</t>
+          <t>19862</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31081</t>
+          <t>31945</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18702</t>
+          <t>19080</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31893</t>
+          <t>32316</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41735</t>
+          <t>41776</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59565</t>
+          <t>60009</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>49,09%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7118</t>
+          <t>7525</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17103</t>
+          <t>17310</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14085</t>
+          <t>13783</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26529</t>
+          <t>26703</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23592</t>
+          <t>23580</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>40072</t>
+          <t>38864</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>31,79%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62256</t>
+          <t>61790</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78099</t>
+          <t>77504</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61193</t>
+          <t>61585</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>78274</t>
+          <t>77989</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>128619</t>
+          <t>128597</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>151748</t>
+          <t>151542</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,4%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16118</t>
+          <t>15433</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29839</t>
+          <t>28890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24025</t>
+          <t>24382</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40877</t>
+          <t>40711</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>43976</t>
+          <t>44047</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>64579</t>
+          <t>64910</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,16%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6994</t>
+          <t>6814</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18030</t>
+          <t>17640</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>5379</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14480</t>
+          <t>14900</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14319</t>
+          <t>14411</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28076</t>
+          <t>28169</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16436</t>
+          <t>17093</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29433</t>
+          <t>29626</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18100</t>
+          <t>17986</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30466</t>
+          <t>30408</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>38175</t>
+          <t>37910</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>56860</t>
+          <t>55892</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,09%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30437</t>
+          <t>29633</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43948</t>
+          <t>43437</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31014</t>
+          <t>30791</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44823</t>
+          <t>44227</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>64034</t>
+          <t>65187</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83537</t>
+          <t>84481</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>60,59%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4364</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13225</t>
+          <t>13130</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>5677</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15058</t>
+          <t>15711</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>12190</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25667</t>
+          <t>25386</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37908</t>
+          <t>37968</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51947</t>
+          <t>52034</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>48010</t>
+          <t>47311</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62764</t>
+          <t>62217</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90029</t>
+          <t>91061</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>111299</t>
+          <t>111370</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,61%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13584</t>
+          <t>13573</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25939</t>
+          <t>25436</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11823</t>
+          <t>12254</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24932</t>
+          <t>24991</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28312</t>
+          <t>28706</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45907</t>
+          <t>46554</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8495</t>
+          <t>8443</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20016</t>
+          <t>19755</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>4672</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14858</t>
+          <t>14898</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16340</t>
+          <t>15588</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>31081</t>
+          <t>31146</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16060</t>
+          <t>16332</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28086</t>
+          <t>27891</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17747</t>
+          <t>17264</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29332</t>
+          <t>28589</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>36558</t>
+          <t>37701</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>53340</t>
+          <t>54428</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>60,04%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>10665</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22079</t>
+          <t>21813</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,82 +2684,82 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
+          <t>24,29%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>49,69%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>13510</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>9052</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>19257</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>28,9%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>19,36%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>41,19%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>29379</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>21397</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>36966</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>32,41%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t>23,6%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>50,29%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>13510</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>8468</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>18255</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>28,9%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>18,11%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>39,05%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>29379</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>22729</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>37185</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>32,41%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>25,07%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,78%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2863</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10232</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5703</t>
+          <t>6036</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15704</t>
+          <t>15177</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10568</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23038</t>
+          <t>22424</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16427</t>
+          <t>16365</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28951</t>
+          <t>28303</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15854</t>
+          <t>16020</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>28430</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>36100</t>
+          <t>35655</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>53179</t>
+          <t>53519</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>46,05%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21167</t>
+          <t>21014</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>34018</t>
+          <t>33362</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>25538</t>
+          <t>24301</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37965</t>
+          <t>37776</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,47 +3175,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>40,34%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>62,7%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>58800</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>49265</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>67573</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>50,59%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>42,39%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>63,02%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>58800</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>50416</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>68359</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>50,59%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>43,38%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>58,14%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11345</t>
+          <t>11252</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3431</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11645</t>
+          <t>11263</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>8284</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>19934</t>
+          <t>19756</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>50134</t>
+          <t>51454</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>70100</t>
+          <t>70996</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>49067</t>
+          <t>47340</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>67497</t>
+          <t>67392</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,47 +3518,47 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
+          <t>46,24%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>118016</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>103612</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>131730</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>41,49%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>36,42%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>46,31%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>118016</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>104422</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>132680</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>41,49%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>36,71%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>46,64%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>53192</t>
+          <t>53256</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>73293</t>
+          <t>72947</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>56339</t>
+          <t>55875</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>75839</t>
+          <t>76394</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>114893</t>
+          <t>115457</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10098</t>
+          <t>10284</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22657</t>
+          <t>22374</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15839</t>
+          <t>15371</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>29981</t>
+          <t>29994</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>28460</t>
+          <t>29214</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>47787</t>
+          <t>48298</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,98%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>105787</t>
+          <t>106537</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>125597</t>
+          <t>124941</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>113664</t>
+          <t>113117</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>133699</t>
+          <t>133215</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>227757</t>
+          <t>226739</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>254091</t>
+          <t>253049</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,48%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>25403</t>
+          <t>25688</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>42485</t>
+          <t>42234</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>28139</t>
+          <t>29419</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>47729</t>
+          <t>47693</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>59388</t>
+          <t>59211</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>83409</t>
+          <t>83052</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>9136</t>
+          <t>8879</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>20956</t>
+          <t>21445</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>5368</t>
+          <t>5592</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>16409</t>
+          <t>16391</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>16262</t>
+          <t>16698</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>32157</t>
+          <t>32990</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>358991</t>
+          <t>359659</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>402388</t>
+          <t>402182</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>374653</t>
+          <t>373723</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>421053</t>
+          <t>418506</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>747571</t>
+          <t>745526</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>811049</t>
+          <t>809093</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,28%</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>223365</t>
+          <t>223314</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>264601</t>
+          <t>263770</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>238411</t>
+          <t>242236</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>283920</t>
+          <t>286961</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>473770</t>
+          <t>472162</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>533903</t>
+          <t>533286</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,44%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>72452</t>
+          <t>73045</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>101619</t>
+          <t>102445</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>80972</t>
+          <t>80006</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>110794</t>
+          <t>111102</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>161727</t>
+          <t>163777</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>200764</t>
+          <t>204858</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20947</t>
+          <t>21127</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32733</t>
+          <t>32929</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28273</t>
+          <t>28176</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41544</t>
+          <t>41107</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52736</t>
+          <t>51488</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70681</t>
+          <t>70955</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>58,24%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16071</t>
+          <t>15884</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27346</t>
+          <t>27258</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14677</t>
+          <t>15431</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27489</t>
+          <t>27468</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33720</t>
+          <t>34404</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51894</t>
+          <t>51297</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,1%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5019</t>
+          <t>5132</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13847</t>
+          <t>13948</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5668</t>
+          <t>5094</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14797</t>
+          <t>14249</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12462</t>
+          <t>12074</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25201</t>
+          <t>25017</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,53%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52545</t>
+          <t>53124</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>68179</t>
+          <t>68717</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>59675</t>
+          <t>59181</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76113</t>
+          <t>75410</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>117420</t>
+          <t>118183</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>140803</t>
+          <t>140700</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,85%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23137</t>
+          <t>24061</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37374</t>
+          <t>37691</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17828</t>
+          <t>19044</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31884</t>
+          <t>33732</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>46025</t>
+          <t>45500</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>66439</t>
+          <t>66125</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7383</t>
+          <t>7359</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17905</t>
+          <t>18405</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11823</t>
+          <t>11671</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23361</t>
+          <t>23894</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>22243</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38234</t>
+          <t>38548</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39309</t>
+          <t>40083</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52509</t>
+          <t>52678</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45624</t>
+          <t>45566</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>57450</t>
+          <t>57485</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>89051</t>
+          <t>89208</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>105914</t>
+          <t>106149</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,63%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13588</t>
+          <t>13431</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26533</t>
+          <t>26138</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10573</t>
+          <t>10668</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22434</t>
+          <t>22449</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28006</t>
+          <t>27708</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44424</t>
+          <t>44963</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,88%</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>664</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>701</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6364</t>
+          <t>6330</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49606</t>
+          <t>49313</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62198</t>
+          <t>62511</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44749</t>
+          <t>45303</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60432</t>
+          <t>60205</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>99552</t>
+          <t>99799</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>118832</t>
+          <t>119008</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,14%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7640</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19066</t>
+          <t>18840</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10680</t>
+          <t>10700</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22273</t>
+          <t>22676</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21191</t>
+          <t>21031</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37281</t>
+          <t>37059</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,71%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>3197</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12320</t>
+          <t>12291</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>6461</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18278</t>
+          <t>17694</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12090</t>
+          <t>11905</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>25743</t>
+          <t>25447</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,28%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22434</t>
+          <t>22602</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32555</t>
+          <t>33008</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26970</t>
+          <t>27505</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37259</t>
+          <t>37232</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>52310</t>
+          <t>52859</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>66865</t>
+          <t>67591</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>75,28%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16167</t>
+          <t>15696</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3811</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12067</t>
+          <t>11879</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>12594</t>
+          <t>11763</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>25024</t>
+          <t>25020</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>2399</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>9154</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10889</t>
+          <t>11109</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7017</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17477</t>
+          <t>17626</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>33801</t>
+          <t>33615</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>44603</t>
+          <t>44115</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>43295</t>
+          <t>44041</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>53129</t>
+          <t>53153</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>81653</t>
+          <t>81636</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>95765</t>
+          <t>95953</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,66%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13211</t>
+          <t>13247</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>2256</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9787</t>
+          <t>9981</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>8563</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20224</t>
+          <t>20313</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3031</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>11063</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>777</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7618</t>
+          <t>7458</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>15585</t>
+          <t>15364</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>66068</t>
+          <t>66255</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>84758</t>
+          <t>85155</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>58307</t>
+          <t>58133</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>77642</t>
+          <t>77760</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>130613</t>
+          <t>129749</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>157760</t>
+          <t>156801</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>55,82%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>36806</t>
+          <t>37470</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>54518</t>
+          <t>55826</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>44985</t>
+          <t>44921</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>63153</t>
+          <t>63817</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>86503</t>
+          <t>87471</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>112482</t>
+          <t>113263</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>40,32%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9717</t>
+          <t>9716</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22136</t>
+          <t>21404</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15999</t>
+          <t>16090</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>31241</t>
+          <t>30107</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>28230</t>
+          <t>28747</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>46564</t>
+          <t>47380</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>116153</t>
+          <t>115416</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>134371</t>
+          <t>132953</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>126640</t>
+          <t>126424</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>143668</t>
+          <t>143239</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>247908</t>
+          <t>248012</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>271432</t>
+          <t>271864</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8349,12 +8349,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,15%</t>
         </is>
       </c>
     </row>
@@ -8377,12 +8377,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>21772</t>
+          <t>21935</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>37698</t>
+          <t>38231</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>21623</t>
+          <t>21531</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>37920</t>
+          <t>37797</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>48500</t>
+          <t>48056</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>70107</t>
+          <t>70505</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8462,12 +8462,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,04%</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6032</t>
+          <t>5797</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15711</t>
+          <t>16622</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3056</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>11011</t>
+          <t>10507</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>10614</t>
+          <t>10697</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>23114</t>
+          <t>23365</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -8720,12 +8720,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>439118</t>
+          <t>437997</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>478984</t>
+          <t>479318</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>472449</t>
+          <t>470904</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>515004</t>
+          <t>513778</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>924459</t>
+          <t>924272</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>983019</t>
+          <t>981435</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8805,12 +8805,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,86%</t>
         </is>
       </c>
     </row>
@@ -8833,12 +8833,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>160046</t>
+          <t>158543</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>196175</t>
+          <t>197663</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8848,12 +8848,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8868,12 +8868,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>154001</t>
+          <t>156565</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>192618</t>
+          <t>193426</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8883,12 +8883,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>325908</t>
+          <t>324861</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>379028</t>
+          <t>378203</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,15%</t>
         </is>
       </c>
     </row>
@@ -8946,12 +8946,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>53836</t>
+          <t>52900</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>79214</t>
+          <t>77780</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>64530</t>
+          <t>63987</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>92369</t>
+          <t>91419</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>124306</t>
+          <t>124477</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>162039</t>
+          <t>159978</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -9412,12 +9412,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65845</t>
+          <t>66801</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72462</t>
+          <t>72612</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>70378</t>
+          <t>70192</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78063</t>
+          <t>78095</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9482,12 +9482,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>140432</t>
+          <t>139626</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>149469</t>
+          <t>149416</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9497,12 +9497,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -9525,12 +9525,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>575</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6082</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>470</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8212</t>
+          <t>7862</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9610,12 +9610,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7418</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9708,12 +9708,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>735</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8840</t>
+          <t>8600</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -9868,12 +9868,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40185</t>
+          <t>36238</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>108497</t>
+          <t>107738</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>96658</t>
+          <t>96900</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112747</t>
+          <t>112680</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9938,12 +9938,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>120708</t>
+          <t>126141</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>215538</t>
+          <t>215317</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9953,12 +9953,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,36%</t>
         </is>
       </c>
     </row>
@@ -9981,12 +9981,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13285</t>
+          <t>13831</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>85106</t>
+          <t>89102</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11414</t>
+          <t>11043</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26161</t>
+          <t>25502</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29490</t>
+          <t>29932</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>127956</t>
+          <t>121876</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10066,12 +10066,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>47,75%</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>1644</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>10322</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10235</t>
+          <t>9570</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10164,12 +10164,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4777</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16198</t>
+          <t>15194</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10179,12 +10179,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -10324,12 +10324,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36523</t>
+          <t>36593</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47496</t>
+          <t>47648</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47209</t>
+          <t>47916</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>58065</t>
+          <t>58592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10394,12 +10394,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>88329</t>
+          <t>88398</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>103382</t>
+          <t>103145</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10409,12 +10409,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,23%</t>
         </is>
       </c>
     </row>
@@ -10437,12 +10437,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7763</t>
+          <t>7216</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18230</t>
+          <t>17119</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3487</t>
+          <t>3462</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11518</t>
+          <t>11358</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10507,12 +10507,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12727</t>
+          <t>12850</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25762</t>
+          <t>25078</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -10550,12 +10550,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1766</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>7520</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3609</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12259</t>
+          <t>12343</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10620,12 +10620,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5888</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15837</t>
+          <t>16114</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10635,12 +10635,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -10780,12 +10780,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47984</t>
+          <t>46871</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60473</t>
+          <t>60071</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57051</t>
+          <t>57262</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71137</t>
+          <t>71897</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>110130</t>
+          <t>110381</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>128461</t>
+          <t>128949</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,96%</t>
         </is>
       </c>
     </row>
@@ -10893,12 +10893,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14963</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13159</t>
+          <t>13604</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>9774</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24227</t>
+          <t>24156</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10978,12 +10978,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -11006,12 +11006,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2724</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>11594</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12695</t>
+          <t>12804</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7093</t>
+          <t>6740</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20054</t>
+          <t>19154</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -11236,12 +11236,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22335</t>
+          <t>22724</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29589</t>
+          <t>29779</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11251,12 +11251,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11271,12 +11271,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33475</t>
+          <t>33356</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39082</t>
+          <t>39068</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11286,12 +11286,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11306,12 +11306,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>57925</t>
+          <t>57690</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>67313</t>
+          <t>67347</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11321,12 +11321,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,52%</t>
         </is>
       </c>
     </row>
@@ -11349,12 +11349,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4377</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11382</t>
+          <t>11235</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11364,12 +11364,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11384,12 +11384,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>7363</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11399,12 +11399,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11419,12 +11419,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>16716</t>
+          <t>16750</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11434,12 +11434,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -11467,7 +11467,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11482,7 +11482,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11537,7 +11537,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2894</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11552,7 +11552,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -11692,12 +11692,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30309</t>
+          <t>29748</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>39371</t>
+          <t>38948</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11727,12 +11727,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>38964</t>
+          <t>40111</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>48945</t>
+          <t>49076</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11762,12 +11762,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>73168</t>
+          <t>73333</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>85768</t>
+          <t>86255</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11777,12 +11777,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>84,27%</t>
         </is>
       </c>
     </row>
@@ -11805,12 +11805,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8283</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11840,12 +11840,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>3440</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11811</t>
+          <t>11474</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11875,12 +11875,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6711</t>
+          <t>6897</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16362</t>
+          <t>16616</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11890,12 +11890,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -11918,12 +11918,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11216</t>
+          <t>11180</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11953,12 +11953,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9090</t>
+          <t>9049</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11968,12 +11968,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11988,12 +11988,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7358</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16802</t>
+          <t>16917</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12003,12 +12003,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -12148,12 +12148,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>63637</t>
+          <t>63781</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>82512</t>
+          <t>82580</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12183,12 +12183,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>65140</t>
+          <t>64388</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>91713</t>
+          <t>91273</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12218,12 +12218,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>133123</t>
+          <t>133625</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>167118</t>
+          <t>168051</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>60,42%</t>
         </is>
       </c>
     </row>
@@ -12261,12 +12261,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17765</t>
+          <t>17864</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>33162</t>
+          <t>33622</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12296,12 +12296,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>28647</t>
+          <t>30081</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>55874</t>
+          <t>55151</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12331,12 +12331,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>52667</t>
+          <t>51976</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>82694</t>
+          <t>83050</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,86%</t>
         </is>
       </c>
     </row>
@@ -12374,12 +12374,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18411</t>
+          <t>18094</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>33459</t>
+          <t>33139</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12409,12 +12409,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>27182</t>
+          <t>26760</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>48781</t>
+          <t>47211</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12444,12 +12444,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>50369</t>
+          <t>49402</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>77024</t>
+          <t>76205</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,4%</t>
         </is>
       </c>
     </row>
@@ -12604,12 +12604,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>93267</t>
+          <t>93788</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>109409</t>
+          <t>109829</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12639,12 +12639,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>112325</t>
+          <t>110821</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>130421</t>
+          <t>130792</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12654,12 +12654,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12674,12 +12674,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>211179</t>
+          <t>209959</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>236067</t>
+          <t>234996</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,48%</t>
         </is>
       </c>
     </row>
@@ -12717,12 +12717,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>15975</t>
+          <t>15705</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>31035</t>
+          <t>30514</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12752,12 +12752,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>19104</t>
+          <t>18163</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>35596</t>
+          <t>35074</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12767,12 +12767,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12787,12 +12787,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>38500</t>
+          <t>39232</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>61343</t>
+          <t>61293</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -12830,12 +12830,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12144</t>
+          <t>12690</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12865,12 +12865,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4678</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>15619</t>
+          <t>15195</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12900,12 +12900,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>10189</t>
+          <t>9508</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>23009</t>
+          <t>24107</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -13060,12 +13060,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>423296</t>
+          <t>410265</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>517636</t>
+          <t>517139</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13075,12 +13075,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>558493</t>
+          <t>558039</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>605025</t>
+          <t>605183</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13110,12 +13110,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13130,12 +13130,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1005769</t>
+          <t>999638</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1107058</t>
+          <t>1106032</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13145,12 +13145,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,57%</t>
         </is>
       </c>
     </row>
@@ -13173,12 +13173,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>94219</t>
+          <t>91954</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>194047</t>
+          <t>204289</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13208,12 +13208,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>92074</t>
+          <t>91371</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>130986</t>
+          <t>130487</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13243,12 +13243,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>195725</t>
+          <t>198797</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>303754</t>
+          <t>307113</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -13286,12 +13286,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>42850</t>
+          <t>43018</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>66454</t>
+          <t>66814</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13321,12 +13321,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>56054</t>
+          <t>54324</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>85387</t>
+          <t>85544</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>105277</t>
+          <t>106374</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>143872</t>
+          <t>143721</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
